--- a/diseases/d030/2015-2019.xlsx
+++ b/diseases/d030/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6520,6 +6585,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6668,6 +6738,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6816,6 +6891,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6964,6 +7044,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7112,6 +7197,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7260,6 +7350,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7408,6 +7503,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7556,6 +7656,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7704,6 +7809,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7852,6 +7962,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8000,6 +8115,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8148,6 +8268,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8296,6 +8421,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8444,6 +8574,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8592,6 +8727,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8740,6 +8880,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8888,6 +9033,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9036,6 +9186,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9184,6 +9339,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9332,6 +9492,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9480,6 +9645,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13300,6 +13470,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13448,6 +13623,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13596,6 +13776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13744,6 +13929,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13892,6 +14082,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14040,6 +14235,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14188,6 +14388,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14336,6 +14541,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14484,6 +14694,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14632,6 +14847,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14780,6 +15000,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14928,6 +15153,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15076,6 +15306,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15224,6 +15459,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15372,6 +15612,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15520,6 +15765,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15668,6 +15918,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15816,6 +16071,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15964,6 +16224,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16112,6 +16377,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16260,6 +16530,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16408,6 +16683,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16556,6 +16836,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16704,6 +16989,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16852,6 +17142,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16998,6 +17293,11 @@
       <c r="S116" t="inlineStr">
         <is>
           <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">

--- a/diseases/d030/2015-2019.xlsx
+++ b/diseases/d030/2015-2019.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.001445859780518485</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.001879617714674031</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.001951910703699955</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0.001951910703699955</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0.002313375648829577</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0.001228980813440713</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0.002241082659803652</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.002096496681751804</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.002385668637855501</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0.001879617714674031</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0.001590445758570334</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0.002024203692725879</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0.00107733854286371</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,9 +2565,9 @@
       <c r="R15" t="n">
         <v>0.0004852450753544841</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2772,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2905,9 +2700,9 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2917,22 +2712,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3041,9 +2826,9 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3053,22 +2838,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3177,9 +2952,9 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3189,22 +2964,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3313,9 +3078,9 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3325,22 +3090,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3449,9 +3204,9 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3461,22 +3216,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3585,9 +3330,9 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3597,22 +3342,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3721,9 +3456,9 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3733,22 +3468,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3857,9 +3582,9 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3869,22 +3594,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3993,9 +3708,9 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4005,22 +3720,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4129,9 +3834,9 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4141,22 +3846,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4265,9 +3960,9 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4277,22 +3972,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4401,9 +4086,9 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4413,22 +4098,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4537,9 +4212,9 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4549,22 +4224,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4673,9 +4338,9 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4685,22 +4350,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4809,9 +4464,9 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4821,22 +4476,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4945,9 +4590,9 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4957,22 +4602,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5081,9 +4716,9 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5093,22 +4728,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5217,9 +4842,9 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5229,22 +4854,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5353,9 +4968,9 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5365,22 +4980,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5489,9 +5094,9 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5501,22 +5106,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5625,9 +5220,9 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5637,22 +5232,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5761,9 +5346,9 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5773,22 +5358,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5897,9 +5472,9 @@
       <c r="R38" t="n">
         <v>0.008860142648296638</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5909,22 +5484,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6033,9 +5598,9 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6045,22 +5610,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6169,9 +5724,9 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6181,22 +5736,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6305,9 +5850,9 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6317,22 +5862,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6441,9 +5976,9 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6453,22 +5988,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6580,11 +6105,6 @@
       <c r="R43" t="n">
         <v>0.001292806251436451</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6597,22 +6117,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6733,11 +6243,6 @@
       <c r="R44" t="n">
         <v>0.0007182256952424729</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6750,22 +6255,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6886,11 +6381,6 @@
       <c r="R45" t="n">
         <v>0.00107733854286371</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6903,22 +6393,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7039,11 +6519,6 @@
       <c r="R46" t="n">
         <v>0.001651919099057688</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7056,22 +6531,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7192,11 +6657,6 @@
       <c r="R47" t="n">
         <v>0.0008618708342909675</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7209,22 +6669,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7345,11 +6795,6 @@
       <c r="R48" t="n">
         <v>0.0009336934038152149</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7362,22 +6807,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7498,11 +6933,6 @@
       <c r="R49" t="n">
         <v>0.001436451390484946</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7515,22 +6945,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7651,11 +7071,6 @@
       <c r="R50" t="n">
         <v>0.001364628820960699</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7668,22 +7083,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7804,11 +7209,6 @@
       <c r="R51" t="n">
         <v>0.00107733854286371</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7821,22 +7221,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7957,11 +7347,6 @@
       <c r="R52" t="n">
         <v>0.0005745805561939783</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7974,22 +7359,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8110,11 +7485,6 @@
       <c r="R53" t="n">
         <v>0.001005515973339462</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8127,22 +7497,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8263,11 +7623,6 @@
       <c r="R54" t="n">
         <v>0.001428459192492018</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8280,22 +7635,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8416,11 +7761,6 @@
       <c r="R55" t="n">
         <v>0.0003571147981230046</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8433,22 +7773,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8569,11 +7899,6 @@
       <c r="R56" t="n">
         <v>0.0007856525558706101</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8586,22 +7911,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8722,11 +8037,6 @@
       <c r="R57" t="n">
         <v>0.0003571147981230046</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8739,22 +8049,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8875,11 +8175,6 @@
       <c r="R58" t="n">
         <v>0.0002856918384984037</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8892,22 +8187,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9028,11 +8313,6 @@
       <c r="R59" t="n">
         <v>0.0006428066366214084</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9045,22 +8325,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9181,11 +8451,6 @@
       <c r="R60" t="n">
         <v>0.0006428066366214084</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9198,22 +8463,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9334,11 +8589,6 @@
       <c r="R61" t="n">
         <v>0.0003571147981230046</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9351,22 +8601,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9487,11 +8727,6 @@
       <c r="R62" t="n">
         <v>0.0006428066366214084</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9504,22 +8739,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9640,11 +8865,6 @@
       <c r="R63" t="n">
         <v>0.0008570755154952111</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9657,22 +8877,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9790,9 +9000,9 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -9802,22 +9012,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9926,9 +9126,9 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -9938,22 +9138,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10062,9 +9252,9 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10074,22 +9264,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10198,9 +9378,9 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10210,22 +9390,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10334,9 +9504,9 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10346,22 +9516,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10470,9 +9630,9 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -10482,22 +9642,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10606,9 +9756,9 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10618,22 +9768,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10742,9 +9882,9 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -10754,22 +9894,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10878,9 +10008,9 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -10890,22 +10020,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11014,9 +10134,9 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11026,22 +10146,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11150,9 +10260,9 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11162,22 +10272,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11286,9 +10386,9 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -11298,22 +10398,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11422,9 +10512,9 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11434,22 +10524,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11558,9 +10638,9 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -11570,22 +10650,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11694,9 +10764,9 @@
       <c r="R78" t="n">
         <v>0.02484127666276327</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -11706,22 +10776,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11830,9 +10890,9 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -11842,22 +10902,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11966,9 +11016,9 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -11978,22 +11028,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12102,9 +11142,9 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -12114,22 +11154,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12238,9 +11268,9 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12250,22 +11280,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12374,9 +11394,9 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -12386,22 +11406,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12510,9 +11520,9 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -12522,22 +11532,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12646,9 +11646,9 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -12658,22 +11658,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12782,9 +11772,9 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -12794,22 +11784,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12918,9 +11898,9 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -12930,22 +11910,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13054,9 +12024,9 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13066,22 +12036,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13190,9 +12150,9 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13202,22 +12162,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13326,9 +12276,9 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -13338,22 +12288,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13465,11 +12405,6 @@
       <c r="R91" t="n">
         <v>0.0007856525558706101</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13482,22 +12417,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13618,11 +12543,6 @@
       <c r="R92" t="n">
         <v>7.142295962460093e-05</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13635,22 +12555,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13771,11 +12681,6 @@
       <c r="R93" t="n">
         <v>0.000640382521826371</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13788,22 +12693,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13924,11 +12819,6 @@
       <c r="R94" t="n">
         <v>0.0002846144541450537</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13941,22 +12831,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14077,11 +12957,6 @@
       <c r="R95" t="n">
         <v>0.0002134608406087903</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14094,22 +12969,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14230,11 +13095,6 @@
       <c r="R96" t="n">
         <v>0.0004269216812175806</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14247,22 +13107,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14383,11 +13233,6 @@
       <c r="R97" t="n">
         <v>0.0007115361353626344</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14400,22 +13245,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14536,11 +13371,6 @@
       <c r="R98" t="n">
         <v>0.0004269216812175806</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14553,22 +13383,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14689,11 +13509,6 @@
       <c r="R99" t="n">
         <v>0.000640382521826371</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14706,22 +13521,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14842,11 +13647,6 @@
       <c r="R100" t="n">
         <v>0.000640382521826371</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14859,22 +13659,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14995,11 +13785,6 @@
       <c r="R101" t="n">
         <v>0.000640382521826371</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15012,22 +13797,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15148,11 +13923,6 @@
       <c r="R102" t="n">
         <v>0.0004269216812175806</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15165,22 +13935,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15301,11 +14061,6 @@
       <c r="R103" t="n">
         <v>0.0003557680676813172</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15318,22 +14073,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15454,11 +14199,6 @@
       <c r="R104" t="n">
         <v>0.0007826897488988979</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15471,22 +14211,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15607,11 +14337,6 @@
       <c r="R105" t="n">
         <v>0.0002836718484057642</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15624,22 +14349,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15760,11 +14475,6 @@
       <c r="R106" t="n">
         <v>0.0003545898105072052</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15777,22 +14487,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15913,11 +14613,6 @@
       <c r="R107" t="n">
         <v>0.0002127538863043232</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15930,22 +14625,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16066,11 +14751,6 @@
       <c r="R108" t="n">
         <v>0.0003545898105072052</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16083,22 +14763,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16219,11 +14889,6 @@
       <c r="R109" t="n">
         <v>0.0002127538863043232</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16236,22 +14901,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16372,11 +15027,6 @@
       <c r="R110" t="n">
         <v>0.0002127538863043232</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16389,22 +15039,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16525,11 +15165,6 @@
       <c r="R111" t="n">
         <v>0.0007800975831158516</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16542,22 +15177,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -16678,11 +15303,6 @@
       <c r="R112" t="n">
         <v>0.0003545898105072052</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16695,22 +15315,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16831,11 +15441,6 @@
       <c r="R113" t="n">
         <v>0.0004255077726086463</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16848,22 +15453,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16984,11 +15579,6 @@
       <c r="R114" t="n">
         <v>0.0005673436968115284</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17001,22 +15591,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17137,11 +15717,6 @@
       <c r="R115" t="n">
         <v>0.0007800975831158516</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17154,22 +15729,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -17290,11 +15855,6 @@
       <c r="R116" t="n">
         <v>0.0002127538863043232</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17307,22 +15867,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>

--- a/diseases/d030/2015-2019.xlsx
+++ b/diseases/d030/2015-2019.xlsx
@@ -2565,9 +2565,9 @@
       <c r="R15" t="n">
         <v>0.0004852450753544841</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2577,12 +2577,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2700,9 +2710,9 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2712,13 +2722,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2729,6 +2749,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2744,7 +2769,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2826,9 +2855,9 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2838,13 +2867,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -2855,6 +2894,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2870,7 +2914,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2952,9 +3000,9 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2964,13 +3012,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -2981,6 +3039,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2996,7 +3059,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC18" t="inlineStr">
         <is>
           <t>web</t>
@@ -3078,9 +3145,9 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3090,13 +3157,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3107,6 +3184,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
@@ -3122,7 +3204,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC19" t="inlineStr">
         <is>
           <t>web</t>
@@ -3204,9 +3290,9 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3216,13 +3302,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3233,6 +3329,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3248,7 +3349,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3330,9 +3435,9 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3342,13 +3447,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3359,6 +3474,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3374,7 +3494,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3456,9 +3580,9 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3468,13 +3592,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3485,6 +3619,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3500,7 +3639,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3582,9 +3725,9 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3594,13 +3737,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3611,6 +3764,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3626,7 +3784,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3708,9 +3870,9 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3720,13 +3882,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -3737,6 +3909,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3752,7 +3929,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3834,9 +4015,9 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3846,13 +4027,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -3863,6 +4054,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3878,7 +4074,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3960,9 +4160,9 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3972,13 +4172,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -3989,6 +4199,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>web</t>
@@ -4004,7 +4219,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC26" t="inlineStr">
         <is>
           <t>web</t>
@@ -4086,9 +4305,9 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4098,13 +4317,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4115,6 +4344,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>web</t>
@@ -4130,7 +4364,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC27" t="inlineStr">
         <is>
           <t>web</t>
@@ -4212,9 +4450,9 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4224,13 +4462,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4241,6 +4489,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4256,7 +4509,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4338,9 +4595,9 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4350,13 +4607,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4367,6 +4634,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4382,7 +4654,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4464,9 +4740,9 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4476,13 +4752,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>all</t>
@@ -4493,6 +4779,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>web</t>
@@ -4508,7 +4799,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC30" t="inlineStr">
         <is>
           <t>web</t>
@@ -4590,9 +4885,9 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4602,13 +4897,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -4619,6 +4924,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>web</t>
@@ -4634,7 +4944,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC31" t="inlineStr">
         <is>
           <t>web</t>
@@ -4716,9 +5030,9 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4728,13 +5042,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -4745,6 +5069,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4760,7 +5089,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4842,9 +5175,9 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4854,13 +5187,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -4871,6 +5214,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4886,7 +5234,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4968,9 +5320,9 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4980,13 +5332,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -4997,6 +5359,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>web</t>
@@ -5012,7 +5379,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC34" t="inlineStr">
         <is>
           <t>web</t>
@@ -5094,9 +5465,9 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5106,13 +5477,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5123,6 +5504,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5138,7 +5524,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5220,9 +5610,9 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5232,13 +5622,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5249,6 +5649,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5264,7 +5669,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5346,9 +5755,9 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5358,13 +5767,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5375,6 +5794,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5390,7 +5814,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5472,9 +5900,9 @@
       <c r="R38" t="n">
         <v>0.008860142648296638</v>
       </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5484,13 +5912,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5501,6 +5939,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5516,7 +5959,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5598,9 +6045,9 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5610,13 +6057,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -5627,6 +6084,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5642,7 +6104,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5724,9 +6190,9 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5736,13 +6202,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -5753,6 +6229,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5768,7 +6249,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5850,9 +6335,9 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5862,13 +6347,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -5879,6 +6374,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5894,7 +6394,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5976,9 +6480,9 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5988,13 +6492,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -6005,6 +6519,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>web</t>
@@ -6020,7 +6539,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC42" t="inlineStr">
         <is>
           <t>web</t>
@@ -9000,9 +9523,9 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -9012,13 +9535,23 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>all</t>
@@ -9029,6 +9562,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>web</t>
@@ -9044,7 +9582,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB64" t="inlineStr"/>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC64" t="inlineStr">
         <is>
           <t>web</t>
@@ -9126,9 +9668,9 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -9138,13 +9680,23 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
@@ -9155,6 +9707,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>web</t>
@@ -9170,7 +9727,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB65" t="inlineStr"/>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC65" t="inlineStr">
         <is>
           <t>web</t>
@@ -9252,9 +9813,9 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -9264,13 +9825,23 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -9281,6 +9852,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>web</t>
@@ -9296,7 +9872,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB66" t="inlineStr"/>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC66" t="inlineStr">
         <is>
           <t>web</t>
@@ -9378,9 +9958,9 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -9390,13 +9970,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -9407,6 +9997,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>web</t>
@@ -9422,7 +10017,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB67" t="inlineStr"/>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC67" t="inlineStr">
         <is>
           <t>web</t>
@@ -9504,9 +10103,9 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -9516,13 +10115,23 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -9533,6 +10142,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>web</t>
@@ -9548,7 +10162,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB68" t="inlineStr"/>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC68" t="inlineStr">
         <is>
           <t>web</t>
@@ -9630,9 +10248,9 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9642,13 +10260,23 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -9659,6 +10287,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>web</t>
@@ -9674,7 +10307,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB69" t="inlineStr"/>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC69" t="inlineStr">
         <is>
           <t>web</t>
@@ -9756,9 +10393,9 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9768,13 +10405,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -9785,6 +10432,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>web</t>
@@ -9800,7 +10452,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB70" t="inlineStr"/>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC70" t="inlineStr">
         <is>
           <t>web</t>
@@ -9882,9 +10538,9 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9894,13 +10550,23 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -9911,6 +10577,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>web</t>
@@ -9926,7 +10597,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB71" t="inlineStr"/>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC71" t="inlineStr">
         <is>
           <t>web</t>
@@ -10008,9 +10683,9 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -10020,13 +10695,23 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -10037,6 +10722,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>web</t>
@@ -10052,7 +10742,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC72" t="inlineStr">
         <is>
           <t>web</t>
@@ -10134,9 +10828,9 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -10146,13 +10840,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -10163,6 +10867,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>web</t>
@@ -10178,7 +10887,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC73" t="inlineStr">
         <is>
           <t>web</t>
@@ -10260,9 +10973,9 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -10272,13 +10985,23 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -10289,6 +11012,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>web</t>
@@ -10304,7 +11032,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB74" t="inlineStr"/>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC74" t="inlineStr">
         <is>
           <t>web</t>
@@ -10386,9 +11118,9 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -10398,13 +11130,23 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -10415,6 +11157,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>web</t>
@@ -10430,7 +11177,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB75" t="inlineStr"/>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC75" t="inlineStr">
         <is>
           <t>web</t>
@@ -10512,9 +11263,9 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -10524,13 +11275,23 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -10541,6 +11302,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>web</t>
@@ -10556,7 +11322,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC76" t="inlineStr">
         <is>
           <t>web</t>
@@ -10638,9 +11408,9 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10650,13 +11420,23 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -10667,6 +11447,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>web</t>
@@ -10682,7 +11467,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB77" t="inlineStr"/>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC77" t="inlineStr">
         <is>
           <t>web</t>
@@ -10764,9 +11553,9 @@
       <c r="R78" t="n">
         <v>0.02484127666276327</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10776,13 +11565,23 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -10793,6 +11592,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>web</t>
@@ -10808,7 +11612,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB78" t="inlineStr"/>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC78" t="inlineStr">
         <is>
           <t>web</t>
@@ -10890,9 +11698,9 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10902,13 +11710,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -10919,6 +11737,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>web</t>
@@ -10934,7 +11757,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB79" t="inlineStr"/>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC79" t="inlineStr">
         <is>
           <t>web</t>
@@ -11016,9 +11843,9 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -11028,13 +11855,23 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -11045,6 +11882,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>web</t>
@@ -11060,7 +11902,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC80" t="inlineStr">
         <is>
           <t>web</t>
@@ -11142,9 +11988,9 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -11154,13 +12000,23 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
@@ -11171,6 +12027,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>web</t>
@@ -11186,7 +12047,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC81" t="inlineStr">
         <is>
           <t>web</t>
@@ -11268,9 +12133,9 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -11280,13 +12145,23 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>all</t>
@@ -11297,6 +12172,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>web</t>
@@ -11312,7 +12192,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC82" t="inlineStr">
         <is>
           <t>web</t>
@@ -11394,9 +12278,9 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -11406,13 +12290,23 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>all</t>
@@ -11423,6 +12317,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>web</t>
@@ -11438,7 +12337,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB83" t="inlineStr"/>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC83" t="inlineStr">
         <is>
           <t>web</t>
@@ -11520,9 +12423,9 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -11532,13 +12435,23 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV84" t="inlineStr">
         <is>
           <t>all</t>
@@ -11549,6 +12462,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>web</t>
@@ -11564,7 +12482,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB84" t="inlineStr"/>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC84" t="inlineStr">
         <is>
           <t>web</t>
@@ -11646,9 +12568,9 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11658,13 +12580,23 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>all</t>
@@ -11675,6 +12607,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>web</t>
@@ -11690,7 +12627,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB85" t="inlineStr"/>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC85" t="inlineStr">
         <is>
           <t>web</t>
@@ -11772,9 +12713,9 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11784,13 +12725,23 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
       </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV86" t="inlineStr">
         <is>
           <t>all</t>
@@ -11801,6 +12752,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>web</t>
@@ -11816,7 +12772,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB86" t="inlineStr"/>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC86" t="inlineStr">
         <is>
           <t>web</t>
@@ -11898,9 +12858,9 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11910,13 +12870,23 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
       </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV87" t="inlineStr">
         <is>
           <t>all</t>
@@ -11927,6 +12897,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>web</t>
@@ -11942,7 +12917,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB87" t="inlineStr"/>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC87" t="inlineStr">
         <is>
           <t>web</t>
@@ -12024,9 +13003,9 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -12036,13 +13015,23 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>all</t>
@@ -12053,6 +13042,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>web</t>
@@ -12068,7 +13062,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB88" t="inlineStr"/>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC88" t="inlineStr">
         <is>
           <t>web</t>
@@ -12150,9 +13148,9 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -12162,13 +13160,23 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
       </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV89" t="inlineStr">
         <is>
           <t>all</t>
@@ -12179,6 +13187,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>web</t>
@@ -12194,7 +13207,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB89" t="inlineStr"/>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC89" t="inlineStr">
         <is>
           <t>web</t>
@@ -12276,9 +13293,9 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -12288,13 +13305,23 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV90" t="inlineStr">
         <is>
           <t>all</t>
@@ -12305,6 +13332,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>web</t>
@@ -12320,7 +13352,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC90" t="inlineStr">
         <is>
           <t>web</t>
